--- a/data-source/卷轴数据.xlsx
+++ b/data-source/卷轴数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jasonX\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9436952-CB83-423C-A0D4-4D5E7DB041D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6730A70A-104E-41D7-8785-DD68709218DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>卷轴</t>
   </si>
@@ -187,6 +187,30 @@
   </si>
   <si>
     <t>诅咒附近的敌人，使其受到的治疗效果降低100%，持续30秒</t>
+  </si>
+  <si>
+    <t>1级火焰卷轴</t>
+  </si>
+  <si>
+    <t>2级火焰卷轴</t>
+  </si>
+  <si>
+    <t>3级火焰卷轴</t>
+  </si>
+  <si>
+    <t>4级火焰卷轴</t>
+  </si>
+  <si>
+    <t>对附近敌人造成40点周期性火焰伤害：10*4点燃</t>
+  </si>
+  <si>
+    <t>对附近敌人造成80点周期性火焰伤害：10*8点燃</t>
+  </si>
+  <si>
+    <t>对附近敌人造成160点周期性火焰伤害：10*16点燃</t>
+  </si>
+  <si>
+    <t>对附近敌人造成320点周期性火焰伤害：10*32点燃</t>
   </si>
 </sst>
 </file>
@@ -313,6 +337,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF9933FF"/>
+      <color rgb="FF02A5E3"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -587,11 +617,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.86328125" customWidth="1"/>
-    <col min="2" max="2" width="33.86328125" customWidth="1"/>
+    <col min="2" max="2" width="36.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -888,6 +918,38 @@
         <v>53</v>
       </c>
     </row>
+    <row r="28" spans="1:5" ht="25.5">
+      <c r="A28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="25.5">
+      <c r="A29" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="25.5">
+      <c r="A30" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="25.5">
+      <c r="A31" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
